--- a/12619425.xlsx
+++ b/12619425.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30431"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="283" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4223A54-4F88-498E-B469-5302310A3BB1}"/>
+  <xr:revisionPtr revIDLastSave="357" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{198C38EB-A997-4217-9A48-5B5EE25545EE}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -216,34 +216,22 @@
     <t>Example row — replace with your own data. Felt a bit tired after evening class.</t>
   </si>
   <si>
-    <t>good</t>
+    <t>Neutral</t>
   </si>
   <si>
-    <t>high</t>
-  </si>
-  <si>
-    <t>top</t>
+    <t>High</t>
   </si>
   <si>
     <t xml:space="preserve">Had a fun hangout </t>
   </si>
   <si>
-    <t>mid</t>
-  </si>
-  <si>
-    <t>low</t>
+    <t>Low</t>
   </si>
   <si>
     <t>too many classes</t>
   </si>
   <si>
-    <t>tired</t>
-  </si>
-  <si>
     <t>did laundry, cooking and house stuff</t>
-  </si>
-  <si>
-    <t>satisfied</t>
   </si>
   <si>
     <t>went to jalander to get some stuff</t>
@@ -252,13 +240,7 @@
     <t>went to play football late at night</t>
   </si>
   <si>
-    <t>Neutral</t>
-  </si>
-  <si>
     <t>played a tournament match</t>
-  </si>
-  <si>
-    <t>Low</t>
   </si>
   <si>
     <t>Unsatisfied</t>
@@ -300,10 +282,22 @@
     <t>the sun was too. bright today</t>
   </si>
   <si>
-    <t>High</t>
+    <t xml:space="preserve">too dry </t>
   </si>
   <si>
-    <t xml:space="preserve">too dry </t>
+    <t>nothing much to do on sunday</t>
+  </si>
+  <si>
+    <t>too hot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">football match </t>
+  </si>
+  <si>
+    <t>a friends birthday</t>
+  </si>
+  <si>
+    <t>cooked tasty chicken</t>
   </si>
 </sst>
 </file>
@@ -1168,13 +1162,13 @@
         <v>58</v>
       </c>
       <c r="L7" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M7" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="M7" s="16" t="s">
+      <c r="N7" s="17" t="s">
         <v>60</v>
-      </c>
-      <c r="N7" s="17" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="15">
@@ -1211,16 +1205,16 @@
         <v>400</v>
       </c>
       <c r="K8" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N8" s="17" t="s">
         <v>62</v>
-      </c>
-      <c r="L8" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="M8" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="N8" s="17" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="30.75">
@@ -1257,16 +1251,16 @@
         <v>380</v>
       </c>
       <c r="K9" s="16" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="L9" s="16" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="M9" s="16" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="30.75">
@@ -1303,16 +1297,16 @@
         <v>410</v>
       </c>
       <c r="K10" s="16" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="L10" s="16" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="M10" s="16" t="s">
         <v>56</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="30.75">
@@ -1358,7 +1352,7 @@
         <v>56</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="15">
@@ -1411,7 +1405,7 @@
         <v>155</v>
       </c>
       <c r="K13" s="16" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="L13" s="16" t="s">
         <v>55</v>
@@ -1420,7 +1414,7 @@
         <v>56</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="15">
@@ -1457,16 +1451,16 @@
         <v>220</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="L14" s="16" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="M14" s="16" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="N14" s="17" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="15">
@@ -1503,16 +1497,16 @@
         <v>330</v>
       </c>
       <c r="K15" s="16" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="L15" s="16" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="M15" s="16" t="s">
         <v>56</v>
       </c>
       <c r="N15" s="17" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="30.75">
@@ -1558,7 +1552,7 @@
         <v>56</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="15">
@@ -1604,7 +1598,7 @@
         <v>56</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="15">
@@ -1641,16 +1635,16 @@
         <v>650</v>
       </c>
       <c r="K18" s="16" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="L18" s="16" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="M18" s="16" t="s">
         <v>56</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="15">
@@ -1696,7 +1690,7 @@
         <v>56</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="15">
@@ -1742,7 +1736,7 @@
         <v>56</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="15">
@@ -1788,7 +1782,7 @@
         <v>56</v>
       </c>
       <c r="N21" s="17" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="15">
@@ -1828,13 +1822,13 @@
         <v>54</v>
       </c>
       <c r="L22" s="16" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="M22" s="16" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="N22" s="17" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="15">
@@ -1874,13 +1868,13 @@
         <v>54</v>
       </c>
       <c r="L23" s="16" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="M23" s="16" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="N23" s="17" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="15">
@@ -1917,16 +1911,16 @@
         <v>290</v>
       </c>
       <c r="K24" s="16" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="L24" s="16" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="M24" s="16" t="s">
         <v>56</v>
       </c>
       <c r="N24" s="17" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="15">
@@ -1963,16 +1957,16 @@
         <v>460</v>
       </c>
       <c r="K25" s="16" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="L25" s="16" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="M25" s="16" t="s">
         <v>56</v>
       </c>
       <c r="N25" s="17" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="15">
@@ -2012,124 +2006,244 @@
         <v>54</v>
       </c>
       <c r="L26" s="16" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="M26" s="16" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="N26" s="17" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="15">
+      <c r="A27" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B27" s="14">
+        <v>400</v>
+      </c>
+      <c r="C27" s="14">
+        <v>30</v>
+      </c>
+      <c r="D27" s="14">
+        <v>190</v>
+      </c>
+      <c r="E27" s="14">
+        <v>20</v>
+      </c>
+      <c r="F27" s="14">
+        <v>0</v>
+      </c>
+      <c r="G27" s="14">
+        <v>0</v>
+      </c>
+      <c r="H27" s="14">
+        <v>440</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
-    </row>
-    <row r="28" spans="1:14">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+        <v>360</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="15">
+      <c r="A28" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B28" s="14">
+        <v>340</v>
+      </c>
+      <c r="C28" s="14">
+        <v>100</v>
+      </c>
+      <c r="D28" s="14">
+        <v>130</v>
+      </c>
+      <c r="E28" s="14">
+        <v>130</v>
+      </c>
+      <c r="F28" s="14">
+        <v>250</v>
+      </c>
+      <c r="G28" s="14">
+        <v>5</v>
+      </c>
+      <c r="H28" s="14">
+        <v>360</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>1310</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
-    </row>
-    <row r="29" spans="1:14">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+        <v>130</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="15">
+      <c r="A29" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B29" s="14">
+        <v>340</v>
+      </c>
+      <c r="C29" s="14">
+        <v>120</v>
+      </c>
+      <c r="D29" s="14">
+        <v>90</v>
+      </c>
+      <c r="E29" s="14">
+        <v>60</v>
+      </c>
+      <c r="F29" s="14">
+        <v>300</v>
+      </c>
+      <c r="G29" s="14">
+        <v>6</v>
+      </c>
+      <c r="H29" s="14">
+        <v>130</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
-    </row>
-    <row r="30" spans="1:14">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+        <v>400</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="15">
+      <c r="A30" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B30" s="14">
+        <v>320</v>
+      </c>
+      <c r="C30" s="14">
+        <v>200</v>
+      </c>
+      <c r="D30" s="14">
+        <v>80</v>
+      </c>
+      <c r="E30" s="14">
+        <v>90</v>
+      </c>
+      <c r="F30" s="14">
+        <v>250</v>
+      </c>
+      <c r="G30" s="14">
+        <v>5</v>
+      </c>
+      <c r="H30" s="14">
+        <v>220</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
-    </row>
-    <row r="31" spans="1:14">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+        <v>280</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="15">
+      <c r="A31" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B31" s="14">
+        <v>350</v>
+      </c>
+      <c r="C31" s="14">
+        <v>60</v>
+      </c>
+      <c r="D31" s="14">
+        <v>120</v>
+      </c>
+      <c r="E31" s="14">
+        <v>30</v>
+      </c>
+      <c r="F31" s="14">
+        <v>250</v>
+      </c>
+      <c r="G31" s="14">
+        <v>5</v>
+      </c>
+      <c r="H31" s="14">
+        <v>240</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+        <v>390</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="13"/>
